--- a/docs/reference/portfolio/statement-template.xlsx
+++ b/docs/reference/portfolio/statement-template.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -430,6 +430,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,7 +489,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5651424.3</v>
+        <v>6196424.3</v>
       </c>
     </row>
     <row r="7">
@@ -526,6 +528,16 @@
           <t>data_posicao</t>
         </is>
       </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t>vencimento</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t>taxa</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -555,6 +567,7 @@
       <c r="G8" s="2" t="n">
         <v>46295</v>
       </c>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -584,6 +597,7 @@
       <c r="G9" s="2" t="n">
         <v>46295</v>
       </c>
+      <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -608,6 +622,7 @@
       <c r="G10" s="2" t="n">
         <v>46295</v>
       </c>
+      <c r="H10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -632,6 +647,7 @@
       <c r="G11" s="2" t="n">
         <v>46295</v>
       </c>
+      <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -661,6 +677,7 @@
       <c r="G12" s="2" t="n">
         <v>46295</v>
       </c>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -690,6 +707,7 @@
       <c r="G13" s="2" t="n">
         <v>46295</v>
       </c>
+      <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -714,6 +732,7 @@
       <c r="G14" s="2" t="n">
         <v>46295</v>
       </c>
+      <c r="H14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -742,6 +761,192 @@
       </c>
       <c r="G15" s="2" t="n">
         <v>46295</v>
+      </c>
+      <c r="H15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CDB BANCO EXEMPLO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CDB-26A00001</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>180000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>180000</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>46827</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>105,00% do CDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LCA BANCO EXEMPLO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LCA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LCA-26A00002</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>120000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>46553</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CDI + 0,50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CRA AGRO EXEMPLO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CRA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CRA-0260000X</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>95000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>95000</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>48136</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>IPCA + 8,74%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DEB ENERGIA EXEMPLO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>debênture</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DEB-EXEM12</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>47741</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15,41% a.a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CDB BANCO EXEMPLO</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CDB-26A00001</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>46827</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>105,00% do CDI</t>
+        </is>
       </c>
     </row>
   </sheetData>
